--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>50.3116</v>
+        <v>57.5877</v>
       </c>
       <c r="E2" t="n">
-        <v>35.4565</v>
+        <v>34.5484</v>
       </c>
       <c r="F2" t="n">
-        <v>14.8545</v>
+        <v>23.0391</v>
       </c>
       <c r="G2" t="n">
-        <v>30.1247</v>
+        <v>66.7933</v>
       </c>
       <c r="H2" t="n">
-        <v>29.5368</v>
+        <v>18.144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5877999999999997</v>
+        <v>48.6489</v>
       </c>
       <c r="J2" t="n">
-        <v>45.9039</v>
+        <v>87.6662</v>
       </c>
       <c r="K2" t="n">
-        <v>35.6793</v>
+        <v>29.2537</v>
       </c>
       <c r="L2" t="n">
-        <v>10.2253</v>
+        <v>58.4122</v>
       </c>
       <c r="M2" t="n">
-        <v>-15.779</v>
+        <v>-20.8729</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.142399999999999</v>
+        <v>-11.1095</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.636700000000001</v>
+        <v>-9.763199999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-14.9711</v>
+        <v>-7.5119</v>
       </c>
       <c r="Q2" t="n">
-        <v>-57.3892</v>
+        <v>-73.5249</v>
       </c>
       <c r="R2" t="n">
-        <v>42.4177</v>
+        <v>66.0132</v>
       </c>
       <c r="S2" t="n">
-        <v>32.3552</v>
+        <v>-34.9867</v>
       </c>
       <c r="T2" t="n">
-        <v>20.3307</v>
+        <v>-23.0732</v>
       </c>
       <c r="U2" t="n">
-        <v>12.0244</v>
+        <v>-11.9135</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8024</v>
+        <v>33.2932</v>
       </c>
       <c r="W2" t="n">
-        <v>26.611</v>
+        <v>43.4807</v>
       </c>
       <c r="X2" t="n">
-        <v>-23.8084</v>
+        <v>-10.1875</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2353</v>
+        <v>56.7905</v>
       </c>
       <c r="E3" t="n">
-        <v>36.5731</v>
+        <v>45.8312</v>
       </c>
       <c r="F3" t="n">
-        <v>13.6627</v>
+        <v>10.9596</v>
       </c>
       <c r="G3" t="n">
-        <v>17.6593</v>
+        <v>22.9809</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2721</v>
+        <v>9.089799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>13.3877</v>
+        <v>13.8909</v>
       </c>
       <c r="J3" t="n">
-        <v>18.7993</v>
+        <v>25.6542</v>
       </c>
       <c r="K3" t="n">
-        <v>5.029500000000001</v>
+        <v>10.871</v>
       </c>
       <c r="L3" t="n">
-        <v>13.7703</v>
+        <v>14.783</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1397</v>
+        <v>-2.673199999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7573000000000002</v>
+        <v>-1.7817</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3822000000000001</v>
+        <v>-0.8918000000000008</v>
       </c>
       <c r="P3" t="n">
-        <v>7.2586</v>
+        <v>9.3329</v>
       </c>
       <c r="Q3" t="n">
-        <v>-27.4468</v>
+        <v>-33.6895</v>
       </c>
       <c r="R3" t="n">
-        <v>34.7056</v>
+        <v>43.0226</v>
       </c>
       <c r="S3" t="n">
-        <v>34.2068</v>
+        <v>37.7864</v>
       </c>
       <c r="T3" t="n">
-        <v>31.2401</v>
+        <v>36.0744</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9668</v>
+        <v>1.7121</v>
       </c>
       <c r="V3" t="n">
-        <v>-8.889099999999999</v>
+        <v>-13.3094</v>
       </c>
       <c r="W3" t="n">
-        <v>13.9806</v>
+        <v>17.7918</v>
       </c>
       <c r="X3" t="n">
-        <v>-22.8699</v>
+        <v>-31.1013</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>41.5059</v>
+        <v>53.6209</v>
       </c>
       <c r="E4" t="n">
-        <v>15.0064</v>
+        <v>41.5654</v>
       </c>
       <c r="F4" t="n">
-        <v>26.4993</v>
+        <v>12.0553</v>
       </c>
       <c r="G4" t="n">
-        <v>30.0705</v>
+        <v>37.0793</v>
       </c>
       <c r="H4" t="n">
-        <v>12.219</v>
+        <v>36.301</v>
       </c>
       <c r="I4" t="n">
-        <v>17.8516</v>
+        <v>0.7776999999999996</v>
       </c>
       <c r="J4" t="n">
-        <v>35.5135</v>
+        <v>55.987</v>
       </c>
       <c r="K4" t="n">
-        <v>20.4654</v>
+        <v>43.848</v>
       </c>
       <c r="L4" t="n">
-        <v>15.0486</v>
+        <v>12.1391</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.4428</v>
+        <v>-18.9076</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.2462</v>
+        <v>-7.5464</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8032</v>
+        <v>-11.3613</v>
       </c>
       <c r="P4" t="n">
-        <v>9.527100000000001</v>
+        <v>-14.1132</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.0667</v>
+        <v>-62.3714</v>
       </c>
       <c r="R4" t="n">
-        <v>45.5935</v>
+        <v>48.2579</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.9799</v>
+        <v>36.9533</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.2797</v>
+        <v>21.9421</v>
       </c>
       <c r="U4" t="n">
-        <v>6.3002</v>
+        <v>15.0111</v>
       </c>
       <c r="V4" t="n">
-        <v>5.888</v>
+        <v>-6.2979</v>
       </c>
       <c r="W4" t="n">
-        <v>25.8392</v>
+        <v>26.0075</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.951</v>
+        <v>-32.3055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>40.6356</v>
+        <v>38.3378</v>
       </c>
       <c r="E5" t="n">
-        <v>22.7834</v>
+        <v>14.2582</v>
       </c>
       <c r="F5" t="n">
-        <v>17.8525</v>
+        <v>24.0793</v>
       </c>
       <c r="G5" t="n">
-        <v>58.5194</v>
+        <v>30.4177</v>
       </c>
       <c r="H5" t="n">
-        <v>14.8956</v>
+        <v>14.6492</v>
       </c>
       <c r="I5" t="n">
-        <v>43.6241</v>
+        <v>15.7683</v>
       </c>
       <c r="J5" t="n">
-        <v>76.7375</v>
+        <v>41.237</v>
       </c>
       <c r="K5" t="n">
-        <v>23.4077</v>
+        <v>26.2677</v>
       </c>
       <c r="L5" t="n">
-        <v>53.3296</v>
+        <v>14.9691</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.2185</v>
+        <v>-10.8192</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.5124</v>
+        <v>-11.6187</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.7059</v>
+        <v>0.7989000000000002</v>
       </c>
       <c r="P5" t="n">
-        <v>-9.753900000000002</v>
+        <v>10.2435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-63.7402</v>
+        <v>-44.8439</v>
       </c>
       <c r="R5" t="n">
-        <v>53.9861</v>
+        <v>55.0873</v>
       </c>
       <c r="S5" t="n">
-        <v>-30.8707</v>
+        <v>-5.879</v>
       </c>
       <c r="T5" t="n">
-        <v>-20.2631</v>
+        <v>-12.1402</v>
       </c>
       <c r="U5" t="n">
-        <v>-10.6073</v>
+        <v>6.2615</v>
       </c>
       <c r="V5" t="n">
-        <v>22.7409</v>
+        <v>3.5559</v>
       </c>
       <c r="W5" t="n">
-        <v>30.0492</v>
+        <v>30.0052</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.3083</v>
+        <v>-26.449</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>27.4249</v>
+        <v>29.2107</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4941</v>
+        <v>14.1956</v>
       </c>
       <c r="F6" t="n">
-        <v>16.9308</v>
+        <v>15.0149</v>
       </c>
       <c r="G6" t="n">
-        <v>28.4275</v>
+        <v>38.6112</v>
       </c>
       <c r="H6" t="n">
-        <v>7.3258</v>
+        <v>13.2685</v>
       </c>
       <c r="I6" t="n">
-        <v>21.1015</v>
+        <v>25.3426</v>
       </c>
       <c r="J6" t="n">
-        <v>33.8109</v>
+        <v>44.0591</v>
       </c>
       <c r="K6" t="n">
-        <v>13.2683</v>
+        <v>20.0588</v>
       </c>
       <c r="L6" t="n">
-        <v>20.543</v>
+        <v>24</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.383800000000001</v>
+        <v>-5.4479</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.942399999999999</v>
+        <v>-6.7904</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5586</v>
+        <v>1.3424</v>
       </c>
       <c r="P6" t="n">
-        <v>16.105</v>
+        <v>17.9828</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.0954</v>
+        <v>-28.454</v>
       </c>
       <c r="R6" t="n">
-        <v>37.2007</v>
+        <v>46.437</v>
       </c>
       <c r="S6" t="n">
-        <v>-11.6119</v>
+        <v>-13.2545</v>
       </c>
       <c r="T6" t="n">
-        <v>-12.2487</v>
+        <v>-11.8606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6368000000000003</v>
+        <v>-1.3935</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.4957</v>
+        <v>-14.1293</v>
       </c>
       <c r="W6" t="n">
-        <v>10.0272</v>
+        <v>10.4513</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.5229</v>
+        <v>-24.5806</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>21.0832</v>
+        <v>23.4679</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6501</v>
+        <v>14.4908</v>
       </c>
       <c r="F7" t="n">
-        <v>6.4333</v>
+        <v>8.976899999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0124</v>
+        <v>2.087200000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6531</v>
+        <v>3.9866</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3591999999999997</v>
+        <v>-1.8994</v>
       </c>
       <c r="J7" t="n">
-        <v>21.5271</v>
+        <v>22.2193</v>
       </c>
       <c r="K7" t="n">
-        <v>7.309</v>
+        <v>9.112</v>
       </c>
       <c r="L7" t="n">
-        <v>14.2182</v>
+        <v>13.1074</v>
       </c>
       <c r="M7" t="n">
-        <v>-18.5147</v>
+        <v>-20.1323</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.655799999999999</v>
+        <v>-5.1253</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.8588</v>
+        <v>-15.0068</v>
       </c>
       <c r="P7" t="n">
-        <v>21.776</v>
+        <v>25.7226</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.7857</v>
+        <v>-19.5765</v>
       </c>
       <c r="R7" t="n">
-        <v>38.5618</v>
+        <v>45.2992</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.4998</v>
+        <v>-10.0778</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.6464</v>
+        <v>-5.8278</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.8537</v>
+        <v>-4.2501</v>
       </c>
       <c r="V7" t="n">
-        <v>4.7945</v>
+        <v>5.7361</v>
       </c>
       <c r="W7" t="n">
-        <v>15.5548</v>
+        <v>17.6758</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.7602</v>
+        <v>-11.9396</v>
       </c>
     </row>
     <row r="8">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>17.7285</v>
+        <v>21.8704</v>
       </c>
       <c r="E8" t="n">
-        <v>9.6343</v>
+        <v>12.3448</v>
       </c>
       <c r="F8" t="n">
-        <v>8.0944</v>
+        <v>9.525499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7239</v>
+        <v>-3.290899999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4242</v>
+        <v>5.1471</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.148300000000001</v>
+        <v>-8.4374</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.391</v>
+        <v>-6.2277</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0885</v>
+        <v>2.1022</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.4796</v>
+        <v>-8.3301</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6668</v>
+        <v>2.937</v>
       </c>
       <c r="N8" t="n">
-        <v>2.335</v>
+        <v>3.0448</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3313999999999997</v>
+        <v>-0.1074000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>16.1051</v>
+        <v>16.8448</v>
       </c>
       <c r="Q8" t="n">
-        <v>-9.526999999999999</v>
+        <v>-11.837</v>
       </c>
       <c r="R8" t="n">
-        <v>25.6321</v>
+        <v>28.6817</v>
       </c>
       <c r="S8" t="n">
-        <v>19.3853</v>
+        <v>22.0814</v>
       </c>
       <c r="T8" t="n">
-        <v>17.935</v>
+        <v>19.9586</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4498</v>
+        <v>2.1229</v>
       </c>
       <c r="V8" t="n">
-        <v>-14.0376</v>
+        <v>-13.7647</v>
       </c>
       <c r="W8" t="n">
-        <v>7.616999999999999</v>
+        <v>10.4511</v>
       </c>
       <c r="X8" t="n">
-        <v>-21.6544</v>
+        <v>-24.2161</v>
       </c>
     </row>
     <row r="9">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>12.4289</v>
+        <v>11.9624</v>
       </c>
       <c r="E9" t="n">
-        <v>1.094699999999999</v>
+        <v>-1.831</v>
       </c>
       <c r="F9" t="n">
-        <v>11.3342</v>
+        <v>13.7934</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.633800000000002</v>
+        <v>-8.215</v>
       </c>
       <c r="H9" t="n">
-        <v>8.2538</v>
+        <v>7.645</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.8874</v>
+        <v>-15.8602</v>
       </c>
       <c r="J9" t="n">
-        <v>8.0451</v>
+        <v>5.5307</v>
       </c>
       <c r="K9" t="n">
-        <v>8.561300000000001</v>
+        <v>9.003500000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5159000000000011</v>
+        <v>-3.472999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.6788</v>
+        <v>-13.7455</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3075000000000002</v>
+        <v>-1.3582</v>
       </c>
       <c r="O9" t="n">
-        <v>-13.3715</v>
+        <v>-12.3871</v>
       </c>
       <c r="P9" t="n">
-        <v>5.671</v>
+        <v>9.3332</v>
       </c>
       <c r="Q9" t="n">
-        <v>-24.2712</v>
+        <v>-25.495</v>
       </c>
       <c r="R9" t="n">
-        <v>29.942</v>
+        <v>34.8278</v>
       </c>
       <c r="S9" t="n">
-        <v>21.326</v>
+        <v>23.8846</v>
       </c>
       <c r="T9" t="n">
-        <v>6.811500000000001</v>
+        <v>7.6818</v>
       </c>
       <c r="U9" t="n">
-        <v>14.5146</v>
+        <v>16.2028</v>
       </c>
       <c r="V9" t="n">
-        <v>-8.9344</v>
+        <v>-13.0404</v>
       </c>
       <c r="W9" t="n">
-        <v>10.5091</v>
+        <v>10.4513</v>
       </c>
       <c r="X9" t="n">
-        <v>-19.4436</v>
+        <v>-23.4917</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9494000000000002</v>
+        <v>6.5481</v>
       </c>
       <c r="E10" t="n">
-        <v>7.2394</v>
+        <v>7.6845</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.2898</v>
+        <v>-1.1364</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.162</v>
+        <v>-1.3352</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.221100000000001</v>
+        <v>-2.8654</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9405999999999998</v>
+        <v>1.5301</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1254</v>
+        <v>3.1174</v>
       </c>
       <c r="K10" t="n">
-        <v>1.595499999999999</v>
+        <v>1.0321</v>
       </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>2.0852</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.287199999999999</v>
+        <v>-4.4529</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.8164</v>
+        <v>-3.8976</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.471</v>
+        <v>-0.5548000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3609</v>
+        <v>2.2761</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.083</v>
+        <v>-5.4631</v>
       </c>
       <c r="R10" t="n">
-        <v>5.4439</v>
+        <v>7.7393</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6665</v>
+        <v>3.2679</v>
       </c>
       <c r="T10" t="n">
-        <v>2.797800000000001</v>
+        <v>3.2493</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1311</v>
+        <v>0.01880000000000011</v>
       </c>
       <c r="V10" t="n">
-        <v>0.08340000000000014</v>
+        <v>2.339</v>
       </c>
       <c r="W10" t="n">
-        <v>5.3993</v>
+        <v>6.781</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.3158</v>
+        <v>-4.442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. SEVILLA</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6006</v>
+        <v>2.2287</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8191999999999999</v>
+        <v>-0.9705999999999992</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2186</v>
+        <v>3.1992</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2045</v>
+        <v>12.4985</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1832</v>
+        <v>-5.2462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02130000000000001</v>
+        <v>17.7443</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6104999999999999</v>
+        <v>20.1055</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6477999999999999</v>
+        <v>2.7392</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>17.3665</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.594</v>
+        <v>-7.607200000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5354</v>
+        <v>-7.9852</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05860000000000001</v>
+        <v>0.3780000000000002</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.9105000000000003</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-22.0803</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>22.9907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0765</v>
+        <v>-10.2937</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2087</v>
+        <v>-6.7084</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1322</v>
+        <v>-3.5853</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.8864999999999996</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>7.7127</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-8.5991</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>P. SEVILLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.177999999999999</v>
+        <v>-0.5964</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.316600000000001</v>
+        <v>-0.8236</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1385999999999998</v>
+        <v>0.2272</v>
       </c>
       <c r="G12" t="n">
-        <v>7.559099999999999</v>
+        <v>-1.2025</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2967</v>
+        <v>-1.1833</v>
       </c>
       <c r="I12" t="n">
-        <v>11.8558</v>
+        <v>-0.01929999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>12.199</v>
+        <v>-0.6145</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5143</v>
+        <v>-0.6518</v>
       </c>
       <c r="L12" t="n">
-        <v>10.685</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.640000000000001</v>
+        <v>-0.588</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.811</v>
+        <v>-0.5316000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1708</v>
+        <v>-0.05649999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9071999999999996</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.61</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>14.5172</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.1835</v>
+        <v>-0.0767</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9589</v>
+        <v>-0.2091</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2247</v>
+        <v>0.1324</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.460900000000001</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.0531</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.5141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>R. LOPEZ DE LA TORRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7682</v>
+        <v>-5.483000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6454</v>
+        <v>-3.6974</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8772</v>
+        <v>-1.7855</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2442</v>
+        <v>1.2003</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1012</v>
+        <v>-0.06930000000000014</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3453</v>
+        <v>1.2697</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5176</v>
+        <v>2.0703</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2601</v>
+        <v>0.5064000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7777</v>
+        <v>1.5639</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7266</v>
+        <v>-0.8699999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1589</v>
+        <v>-0.5759</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5676999999999999</v>
+        <v>-0.2941</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-5.691000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>3.4145</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.163</v>
+        <v>-1.3678</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8861</v>
+        <v>-1.1664</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7231</v>
+        <v>-0.2014</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-3.0392</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-4.1287</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LOPEZ DE LA TORRE</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9259</v>
+        <v>-5.8466</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3877</v>
+        <v>-8.9551</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5381</v>
+        <v>3.1083</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06220000000000003</v>
+        <v>-2.3408</v>
       </c>
       <c r="H14" t="n">
-        <v>1.267</v>
+        <v>-5.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2048</v>
+        <v>2.745400000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2749</v>
+        <v>0.4105999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1256</v>
+        <v>-3.8608</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1493</v>
+        <v>4.271199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2126</v>
+        <v>-2.751399999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1414</v>
+        <v>-1.2256</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.354</v>
+        <v>-1.5257</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0415</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.402600000000001</v>
+        <v>-12.0645</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>7.9673</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4398</v>
+        <v>-3.4509</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2601</v>
+        <v>-4.5403</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1796</v>
+        <v>1.0895</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5068</v>
+        <v>4.0423</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>7.2394</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5068</v>
+        <v>-3.1969</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.9232</v>
+        <v>-15.8405</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.1211</v>
+        <v>-11.2367</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.802</v>
+        <v>-4.604200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.164</v>
+        <v>-10.1242</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2017</v>
+        <v>-2.1265</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.9624</v>
+        <v>-7.9979</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.254600000000001</v>
+        <v>-6.353</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6028000000000001</v>
+        <v>-0.6142</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.6517</v>
+        <v>-5.7389</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.9094</v>
+        <v>-3.7714</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5987</v>
+        <v>-1.5127</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3106</v>
+        <v>-2.2592</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.2171</v>
+        <v>-5.2355</v>
       </c>
       <c r="R15" t="n">
-        <v>7.4855</v>
+        <v>7.511900000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.849</v>
+        <v>0.8524</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5169999999999999</v>
+        <v>-0.5083</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3662</v>
+        <v>1.3609</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.876300000000001</v>
+        <v>-8.844899999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8677999999999999</v>
+        <v>0.8603000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.7441</v>
+        <v>-9.7051</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-23.027</v>
+        <v>-23.2709</v>
       </c>
       <c r="E16" t="n">
-        <v>-32.0228</v>
+        <v>-33.1797</v>
       </c>
       <c r="F16" t="n">
-        <v>8.995699999999999</v>
+        <v>9.9087</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.278099999999999</v>
+        <v>-7.435100000000002</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.3847</v>
+        <v>-4.401899999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.8932</v>
+        <v>-3.0331</v>
       </c>
       <c r="J16" t="n">
-        <v>10.6287</v>
+        <v>9.735800000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>2.734</v>
+        <v>2.2305</v>
       </c>
       <c r="L16" t="n">
-        <v>7.894699999999999</v>
+        <v>7.505399999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-17.9067</v>
+        <v>-17.1711</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.1189</v>
+        <v>-6.6325</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.788</v>
+        <v>-10.5385</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.4855</v>
+        <v>-7.512</v>
       </c>
       <c r="Q16" t="n">
-        <v>-53.7596</v>
+        <v>-53.9487</v>
       </c>
       <c r="R16" t="n">
-        <v>46.2741</v>
+        <v>46.4369</v>
       </c>
       <c r="S16" t="n">
-        <v>-10.3529</v>
+        <v>-10.3916</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.0143</v>
+        <v>-7.9908</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.3385</v>
+        <v>-2.4005</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0892</v>
+        <v>2.0677</v>
       </c>
       <c r="W16" t="n">
-        <v>19.1222</v>
+        <v>19.0243</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.0333</v>
+        <v>-16.9566</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-27.3072</v>
+        <v>-23.6004</v>
       </c>
       <c r="E17" t="n">
-        <v>-29.2334</v>
+        <v>-24.5023</v>
       </c>
       <c r="F17" t="n">
-        <v>1.926</v>
+        <v>0.9015000000000017</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7814</v>
+        <v>26.6492</v>
       </c>
       <c r="H17" t="n">
-        <v>1.533699999999999</v>
+        <v>10.7986</v>
       </c>
       <c r="I17" t="n">
-        <v>12.2482</v>
+        <v>15.8505</v>
       </c>
       <c r="J17" t="n">
-        <v>19.8279</v>
+        <v>33.8701</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3856</v>
+        <v>14.5113</v>
       </c>
       <c r="L17" t="n">
-        <v>15.4424</v>
+        <v>19.3584</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.046799999999999</v>
+        <v>-7.2213</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.8521</v>
+        <v>-3.713</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1943</v>
+        <v>-3.5081</v>
       </c>
       <c r="P17" t="n">
-        <v>-32.4371</v>
+        <v>-36.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-67.36960000000001</v>
+        <v>-78.3053</v>
       </c>
       <c r="R17" t="n">
-        <v>34.9325</v>
+        <v>42.1122</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.8091</v>
+        <v>-19.8759</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.0097</v>
+        <v>-12.8667</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.7999</v>
+        <v>-7.0091</v>
       </c>
       <c r="V17" t="n">
-        <v>6.1575</v>
+        <v>5.8199</v>
       </c>
       <c r="W17" t="n">
-        <v>27.3174</v>
+        <v>32.8005</v>
       </c>
       <c r="X17" t="n">
-        <v>-21.1599</v>
+        <v>-26.9802</v>
       </c>
     </row>
     <row r="18">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>184.5732</v>
+        <v>226.9873</v>
       </c>
       <c r="E18" t="n">
-        <v>69.38579999999996</v>
+        <v>99.7225</v>
       </c>
       <c r="F18" t="n">
-        <v>115.1879</v>
+        <v>127.2628</v>
       </c>
       <c r="G18" t="n">
-        <v>155.806</v>
+        <v>204.3739</v>
       </c>
       <c r="H18" t="n">
-        <v>73.1949</v>
+        <v>98.05089999999998</v>
       </c>
       <c r="I18" t="n">
-        <v>82.61259999999999</v>
+        <v>106.3211</v>
       </c>
       <c r="J18" t="n">
-        <v>272.6195</v>
+        <v>338.468</v>
       </c>
       <c r="K18" t="n">
-        <v>127.1735</v>
+        <v>166.4096</v>
       </c>
       <c r="L18" t="n">
-        <v>145.4488</v>
+        <v>172.0566</v>
       </c>
       <c r="M18" t="n">
-        <v>-116.8138</v>
+        <v>-134.0949</v>
       </c>
       <c r="N18" t="n">
-        <v>-53.979</v>
+        <v>-68.3595</v>
       </c>
       <c r="O18" t="n">
-        <v>-62.8353</v>
+        <v>-65.73519999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>13.60959999999999</v>
+        <v>23.90169999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-407.1666</v>
+        <v>-482.5806</v>
       </c>
       <c r="R18" t="n">
-        <v>420.7757</v>
+        <v>506.4824</v>
       </c>
       <c r="S18" t="n">
-        <v>23.80169999999999</v>
+        <v>15.17139999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>7.822400000000014</v>
+        <v>2.014399999999995</v>
       </c>
       <c r="U18" t="n">
-        <v>15.9793</v>
+        <v>13.1586</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.6449</v>
+        <v>-16.4582</v>
       </c>
       <c r="W18" t="n">
-        <v>196.1086</v>
+        <v>241.8224</v>
       </c>
       <c r="X18" t="n">
-        <v>-204.7534</v>
+        <v>-258.2799</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCAM Murcia.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>57.5877</v>
+        <v>88.5972</v>
       </c>
       <c r="E2" t="n">
-        <v>34.5484</v>
+        <v>55.0402</v>
       </c>
       <c r="F2" t="n">
-        <v>23.0391</v>
+        <v>33.5568</v>
       </c>
       <c r="G2" t="n">
         <v>66.7933</v>
@@ -610,13 +610,13 @@
         <v>66.0132</v>
       </c>
       <c r="S2" t="n">
-        <v>-34.9867</v>
+        <v>-3.977</v>
       </c>
       <c r="T2" t="n">
-        <v>-23.0732</v>
+        <v>-2.5816</v>
       </c>
       <c r="U2" t="n">
-        <v>-11.9135</v>
+        <v>-1.3957</v>
       </c>
       <c r="V2" t="n">
         <v>33.2932</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>56.7905</v>
+        <v>41.7883</v>
       </c>
       <c r="E3" t="n">
-        <v>45.8312</v>
+        <v>21.3655</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9596</v>
+        <v>20.4233</v>
       </c>
       <c r="G3" t="n">
-        <v>22.9809</v>
+        <v>30.4177</v>
       </c>
       <c r="H3" t="n">
-        <v>9.089799999999999</v>
+        <v>14.6492</v>
       </c>
       <c r="I3" t="n">
-        <v>13.8909</v>
+        <v>15.7683</v>
       </c>
       <c r="J3" t="n">
-        <v>25.6542</v>
+        <v>41.237</v>
       </c>
       <c r="K3" t="n">
-        <v>10.871</v>
+        <v>26.2677</v>
       </c>
       <c r="L3" t="n">
-        <v>14.783</v>
+        <v>14.9691</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.673199999999999</v>
+        <v>-10.8192</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7817</v>
+        <v>-11.6187</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8918000000000008</v>
+        <v>0.7989000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>9.3329</v>
+        <v>10.2435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.6895</v>
+        <v>-44.8439</v>
       </c>
       <c r="R3" t="n">
-        <v>43.0226</v>
+        <v>55.0873</v>
       </c>
       <c r="S3" t="n">
-        <v>37.7864</v>
+        <v>-2.4286</v>
       </c>
       <c r="T3" t="n">
-        <v>36.0744</v>
+        <v>-5.0329</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7121</v>
+        <v>2.6045</v>
       </c>
       <c r="V3" t="n">
-        <v>-13.3094</v>
+        <v>3.5559</v>
       </c>
       <c r="W3" t="n">
-        <v>17.7918</v>
+        <v>30.0052</v>
       </c>
       <c r="X3" t="n">
-        <v>-31.1013</v>
+        <v>-26.449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>53.6209</v>
+        <v>41.4029</v>
       </c>
       <c r="E4" t="n">
-        <v>41.5654</v>
+        <v>24.0548</v>
       </c>
       <c r="F4" t="n">
-        <v>12.0553</v>
+        <v>17.3486</v>
       </c>
       <c r="G4" t="n">
-        <v>37.0793</v>
+        <v>38.6112</v>
       </c>
       <c r="H4" t="n">
-        <v>36.301</v>
+        <v>13.2685</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7776999999999996</v>
+        <v>25.3426</v>
       </c>
       <c r="J4" t="n">
-        <v>55.987</v>
+        <v>44.0591</v>
       </c>
       <c r="K4" t="n">
-        <v>43.848</v>
+        <v>20.0588</v>
       </c>
       <c r="L4" t="n">
-        <v>12.1391</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.9076</v>
+        <v>-5.4479</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.5464</v>
+        <v>-6.7904</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.3613</v>
+        <v>1.3424</v>
       </c>
       <c r="P4" t="n">
-        <v>-14.1132</v>
+        <v>17.9828</v>
       </c>
       <c r="Q4" t="n">
-        <v>-62.3714</v>
+        <v>-28.454</v>
       </c>
       <c r="R4" t="n">
-        <v>48.2579</v>
+        <v>46.437</v>
       </c>
       <c r="S4" t="n">
-        <v>36.9533</v>
+        <v>-1.0618</v>
       </c>
       <c r="T4" t="n">
-        <v>21.9421</v>
+        <v>-2.0014</v>
       </c>
       <c r="U4" t="n">
-        <v>15.0111</v>
+        <v>0.9396000000000007</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.2979</v>
+        <v>-14.1293</v>
       </c>
       <c r="W4" t="n">
-        <v>26.0075</v>
+        <v>10.4513</v>
       </c>
       <c r="X4" t="n">
-        <v>-32.3055</v>
+        <v>-24.5806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>38.3378</v>
+        <v>34.5388</v>
       </c>
       <c r="E5" t="n">
-        <v>14.2582</v>
+        <v>19.3058</v>
       </c>
       <c r="F5" t="n">
-        <v>24.0793</v>
+        <v>15.233</v>
       </c>
       <c r="G5" t="n">
-        <v>30.4177</v>
+        <v>2.087200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>14.6492</v>
+        <v>3.9866</v>
       </c>
       <c r="I5" t="n">
-        <v>15.7683</v>
+        <v>-1.8994</v>
       </c>
       <c r="J5" t="n">
-        <v>41.237</v>
+        <v>22.2193</v>
       </c>
       <c r="K5" t="n">
-        <v>26.2677</v>
+        <v>9.112</v>
       </c>
       <c r="L5" t="n">
-        <v>14.9691</v>
+        <v>13.1074</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.8192</v>
+        <v>-20.1323</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.6187</v>
+        <v>-5.1253</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7989000000000002</v>
+        <v>-15.0068</v>
       </c>
       <c r="P5" t="n">
-        <v>10.2435</v>
+        <v>25.7226</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.8439</v>
+        <v>-19.5765</v>
       </c>
       <c r="R5" t="n">
-        <v>55.0873</v>
+        <v>45.2992</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.879</v>
+        <v>0.9929999999999994</v>
       </c>
       <c r="T5" t="n">
-        <v>-12.1402</v>
+        <v>-1.013</v>
       </c>
       <c r="U5" t="n">
-        <v>6.2615</v>
+        <v>2.0062</v>
       </c>
       <c r="V5" t="n">
-        <v>3.5559</v>
+        <v>5.7361</v>
       </c>
       <c r="W5" t="n">
-        <v>30.0052</v>
+        <v>17.6758</v>
       </c>
       <c r="X5" t="n">
-        <v>-26.449</v>
+        <v>-11.9396</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>29.2107</v>
+        <v>32.0644</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1956</v>
+        <v>21.6893</v>
       </c>
       <c r="F6" t="n">
-        <v>15.0149</v>
+        <v>10.3745</v>
       </c>
       <c r="G6" t="n">
-        <v>38.6112</v>
+        <v>22.9809</v>
       </c>
       <c r="H6" t="n">
-        <v>13.2685</v>
+        <v>9.089799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>25.3426</v>
+        <v>13.8909</v>
       </c>
       <c r="J6" t="n">
-        <v>44.0591</v>
+        <v>25.6542</v>
       </c>
       <c r="K6" t="n">
-        <v>20.0588</v>
+        <v>10.871</v>
       </c>
       <c r="L6" t="n">
-        <v>24</v>
+        <v>14.783</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.4479</v>
+        <v>-2.673199999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.7904</v>
+        <v>-1.7817</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3424</v>
+        <v>-0.8918000000000008</v>
       </c>
       <c r="P6" t="n">
-        <v>17.9828</v>
+        <v>9.3329</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.454</v>
+        <v>-33.6895</v>
       </c>
       <c r="R6" t="n">
-        <v>46.437</v>
+        <v>43.0226</v>
       </c>
       <c r="S6" t="n">
-        <v>-13.2545</v>
+        <v>13.0595</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.8606</v>
+        <v>11.9328</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3935</v>
+        <v>1.1266</v>
       </c>
       <c r="V6" t="n">
-        <v>-14.1293</v>
+        <v>-13.3094</v>
       </c>
       <c r="W6" t="n">
-        <v>10.4513</v>
+        <v>17.7918</v>
       </c>
       <c r="X6" t="n">
-        <v>-24.5806</v>
+        <v>-31.1013</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>23.4679</v>
+        <v>30.8011</v>
       </c>
       <c r="E7" t="n">
-        <v>14.4908</v>
+        <v>24.4466</v>
       </c>
       <c r="F7" t="n">
-        <v>8.976899999999999</v>
+        <v>6.354500000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.087200000000001</v>
+        <v>37.0793</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9866</v>
+        <v>36.301</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8994</v>
+        <v>0.7776999999999996</v>
       </c>
       <c r="J7" t="n">
-        <v>22.2193</v>
+        <v>55.987</v>
       </c>
       <c r="K7" t="n">
-        <v>9.112</v>
+        <v>43.848</v>
       </c>
       <c r="L7" t="n">
-        <v>13.1074</v>
+        <v>12.1391</v>
       </c>
       <c r="M7" t="n">
-        <v>-20.1323</v>
+        <v>-18.9076</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.1253</v>
+        <v>-7.5464</v>
       </c>
       <c r="O7" t="n">
-        <v>-15.0068</v>
+        <v>-11.3613</v>
       </c>
       <c r="P7" t="n">
-        <v>25.7226</v>
+        <v>-14.1132</v>
       </c>
       <c r="Q7" t="n">
-        <v>-19.5765</v>
+        <v>-62.3714</v>
       </c>
       <c r="R7" t="n">
-        <v>45.2992</v>
+        <v>48.2579</v>
       </c>
       <c r="S7" t="n">
-        <v>-10.0778</v>
+        <v>14.1332</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.8278</v>
+        <v>4.8238</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.2501</v>
+        <v>9.309699999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>5.7361</v>
+        <v>-6.2979</v>
       </c>
       <c r="W7" t="n">
-        <v>17.6758</v>
+        <v>26.0075</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.9396</v>
+        <v>-32.3055</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>21.8704</v>
+        <v>10.4474</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3448</v>
+        <v>0.3195000000000006</v>
       </c>
       <c r="F8" t="n">
-        <v>9.525499999999999</v>
+        <v>10.1282</v>
       </c>
       <c r="G8" t="n">
         <v>-3.290899999999999</v>
@@ -1078,13 +1078,13 @@
         <v>28.6817</v>
       </c>
       <c r="S8" t="n">
-        <v>22.0814</v>
+        <v>10.6584</v>
       </c>
       <c r="T8" t="n">
-        <v>19.9586</v>
+        <v>7.9329</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1229</v>
+        <v>2.7255</v>
       </c>
       <c r="V8" t="n">
         <v>-13.7647</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>11.9624</v>
+        <v>7.457100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.831</v>
+        <v>2.7151</v>
       </c>
       <c r="F9" t="n">
-        <v>13.7934</v>
+        <v>4.7417</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.215</v>
+        <v>12.4985</v>
       </c>
       <c r="H9" t="n">
-        <v>7.645</v>
+        <v>-5.2462</v>
       </c>
       <c r="I9" t="n">
-        <v>-15.8602</v>
+        <v>17.7443</v>
       </c>
       <c r="J9" t="n">
-        <v>5.5307</v>
+        <v>20.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>9.003500000000001</v>
+        <v>2.7392</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.472999999999999</v>
+        <v>17.3665</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.7455</v>
+        <v>-7.607200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3582</v>
+        <v>-7.9852</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.3871</v>
+        <v>0.3780000000000002</v>
       </c>
       <c r="P9" t="n">
-        <v>9.3332</v>
+        <v>0.9105000000000003</v>
       </c>
       <c r="Q9" t="n">
-        <v>-25.495</v>
+        <v>-22.0803</v>
       </c>
       <c r="R9" t="n">
-        <v>34.8278</v>
+        <v>22.9907</v>
       </c>
       <c r="S9" t="n">
-        <v>23.8846</v>
+        <v>-5.065300000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>7.6818</v>
+        <v>-3.0225</v>
       </c>
       <c r="U9" t="n">
-        <v>16.2028</v>
+        <v>-2.0428</v>
       </c>
       <c r="V9" t="n">
-        <v>-13.0404</v>
+        <v>-0.8864999999999996</v>
       </c>
       <c r="W9" t="n">
-        <v>10.4513</v>
+        <v>7.7127</v>
       </c>
       <c r="X9" t="n">
-        <v>-23.4917</v>
+        <v>-8.5991</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>6.5481</v>
+        <v>4.7797</v>
       </c>
       <c r="E10" t="n">
-        <v>7.6845</v>
+        <v>5.5038</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1364</v>
+        <v>-0.7239999999999995</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3352</v>
@@ -1234,13 +1234,13 @@
         <v>7.7393</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2679</v>
+        <v>1.4996</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2493</v>
+        <v>1.0685</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01880000000000011</v>
+        <v>0.4312</v>
       </c>
       <c r="V10" t="n">
         <v>2.339</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2287</v>
+        <v>3.531499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9705999999999992</v>
+        <v>-3.676699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1992</v>
+        <v>7.208599999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>12.4985</v>
+        <v>-8.215</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.2462</v>
+        <v>7.645</v>
       </c>
       <c r="I11" t="n">
-        <v>17.7443</v>
+        <v>-15.8602</v>
       </c>
       <c r="J11" t="n">
-        <v>20.1055</v>
+        <v>5.5307</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7392</v>
+        <v>9.003500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>17.3665</v>
+        <v>-3.472999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.607200000000001</v>
+        <v>-13.7455</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.9852</v>
+        <v>-1.3582</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3780000000000002</v>
+        <v>-12.3871</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9105000000000003</v>
+        <v>9.3332</v>
       </c>
       <c r="Q11" t="n">
-        <v>-22.0803</v>
+        <v>-25.495</v>
       </c>
       <c r="R11" t="n">
-        <v>22.9907</v>
+        <v>34.8278</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.2937</v>
+        <v>15.4542</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.7084</v>
+        <v>5.8359</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.5853</v>
+        <v>9.6181</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8864999999999996</v>
+        <v>-13.0404</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7127</v>
+        <v>10.4513</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.5991</v>
+        <v>-23.4917</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5964</v>
+        <v>-0.3838</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8236</v>
+        <v>-0.7052</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2272</v>
+        <v>0.3214</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2025</v>
@@ -1390,13 +1390,13 @@
         <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0767</v>
+        <v>0.1359</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2091</v>
+        <v>-0.0907</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1324</v>
+        <v>0.2266</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. LOPEZ DE LA TORRE</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.483000000000001</v>
+        <v>-3.659</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6974</v>
+        <v>-7.1784</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7855</v>
+        <v>3.5193</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2003</v>
+        <v>-2.3408</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.06930000000000014</v>
+        <v>-5.0863</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2697</v>
+        <v>2.745400000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0703</v>
+        <v>0.4105999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5064000000000001</v>
+        <v>-3.8608</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5639</v>
+        <v>4.271199999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8699999999999999</v>
+        <v>-2.751399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5759</v>
+        <v>-1.2256</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2941</v>
+        <v>-1.5257</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2763</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.691000000000001</v>
+        <v>-12.0645</v>
       </c>
       <c r="R13" t="n">
-        <v>3.4145</v>
+        <v>7.9673</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3678</v>
+        <v>-1.2633</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1664</v>
+        <v>-2.7637</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2014</v>
+        <v>1.5004</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.0392</v>
+        <v>4.0423</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0895</v>
+        <v>7.2394</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.1287</v>
+        <v>-3.1969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>R. LOPEZ DE LA TORRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.8466</v>
+        <v>-5.145</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.9551</v>
+        <v>-3.3908</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1083</v>
+        <v>-1.7543</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.3408</v>
+        <v>1.2003</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.0863</v>
+        <v>-0.06930000000000014</v>
       </c>
       <c r="I14" t="n">
-        <v>2.745400000000001</v>
+        <v>1.2697</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4105999999999999</v>
+        <v>2.0703</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.8608</v>
+        <v>0.5064000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.271199999999999</v>
+        <v>1.5639</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.751399999999999</v>
+        <v>-0.8699999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2256</v>
+        <v>-0.5759</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.5257</v>
+        <v>-0.2941</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.0974</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.0645</v>
+        <v>-5.691000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>7.9673</v>
+        <v>3.4145</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4509</v>
+        <v>-1.0298</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.5403</v>
+        <v>-0.8599</v>
       </c>
       <c r="U14" t="n">
+        <v>-0.1699</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-3.0392</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.0895</v>
       </c>
-      <c r="V14" t="n">
-        <v>4.0423</v>
-      </c>
-      <c r="W14" t="n">
-        <v>7.2394</v>
-      </c>
       <c r="X14" t="n">
-        <v>-3.1969</v>
+        <v>-4.1287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.8405</v>
+        <v>-6.816800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.2367</v>
+        <v>-14.6009</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.604200000000001</v>
+        <v>7.7841</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.1242</v>
+        <v>26.6492</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1265</v>
+        <v>10.7986</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.9979</v>
+        <v>15.8505</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.353</v>
+        <v>33.8701</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6142</v>
+        <v>14.5113</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.7389</v>
+        <v>19.3584</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7714</v>
+        <v>-7.2213</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5127</v>
+        <v>-3.713</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2592</v>
+        <v>-3.5081</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2763</v>
+        <v>-36.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.2355</v>
+        <v>-78.3053</v>
       </c>
       <c r="R15" t="n">
-        <v>7.511900000000001</v>
+        <v>42.1122</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8524</v>
+        <v>-3.0925</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5083</v>
+        <v>-2.966</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3609</v>
+        <v>-0.1264</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.844899999999999</v>
+        <v>5.8199</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8603000000000001</v>
+        <v>32.8005</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.7051</v>
+        <v>-26.9802</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-23.2709</v>
+        <v>-10.7793</v>
       </c>
       <c r="E16" t="n">
-        <v>-33.1797</v>
+        <v>-24.1496</v>
       </c>
       <c r="F16" t="n">
-        <v>9.9087</v>
+        <v>13.3703</v>
       </c>
       <c r="G16" t="n">
         <v>-7.435100000000002</v>
@@ -1702,13 +1702,13 @@
         <v>46.4369</v>
       </c>
       <c r="S16" t="n">
-        <v>-10.3916</v>
+        <v>2.1001</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.9908</v>
+        <v>1.0392</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4005</v>
+        <v>1.0607</v>
       </c>
       <c r="V16" t="n">
         <v>2.0677</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.6004</v>
+        <v>-13.9024</v>
       </c>
       <c r="E17" t="n">
-        <v>-24.5023</v>
+        <v>-9.863800000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9015000000000017</v>
+        <v>-4.0382</v>
       </c>
       <c r="G17" t="n">
-        <v>26.6492</v>
+        <v>-10.1242</v>
       </c>
       <c r="H17" t="n">
-        <v>10.7986</v>
+        <v>-2.1265</v>
       </c>
       <c r="I17" t="n">
-        <v>15.8505</v>
+        <v>-7.9979</v>
       </c>
       <c r="J17" t="n">
-        <v>33.8701</v>
+        <v>-6.353</v>
       </c>
       <c r="K17" t="n">
-        <v>14.5113</v>
+        <v>-0.6142</v>
       </c>
       <c r="L17" t="n">
-        <v>19.3584</v>
+        <v>-5.7389</v>
       </c>
       <c r="M17" t="n">
-        <v>-7.2213</v>
+        <v>-3.7714</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.713</v>
+        <v>-1.5127</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.5081</v>
+        <v>-2.2592</v>
       </c>
       <c r="P17" t="n">
-        <v>-36.1931</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-78.3053</v>
+        <v>-5.2355</v>
       </c>
       <c r="R17" t="n">
-        <v>42.1122</v>
+        <v>7.511900000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-19.8759</v>
+        <v>2.7907</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.8667</v>
+        <v>0.8642000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.0091</v>
+        <v>1.9265</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8199</v>
+        <v>-8.844899999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>32.8005</v>
+        <v>0.8603000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-26.9802</v>
+        <v>-9.7051</v>
       </c>
     </row>
     <row r="18">
@@ -1813,25 +1813,25 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>226.9873</v>
+        <v>254.7221</v>
       </c>
       <c r="E18" t="n">
-        <v>99.7225</v>
+        <v>110.8752</v>
       </c>
       <c r="F18" t="n">
-        <v>127.2628</v>
+        <v>143.8478</v>
       </c>
       <c r="G18" t="n">
         <v>204.3739</v>
       </c>
       <c r="H18" t="n">
-        <v>98.05089999999998</v>
+        <v>98.05090000000001</v>
       </c>
       <c r="I18" t="n">
         <v>106.3211</v>
       </c>
       <c r="J18" t="n">
-        <v>338.468</v>
+        <v>338.4680000000001</v>
       </c>
       <c r="K18" t="n">
         <v>166.4096</v>
@@ -1849,25 +1849,25 @@
         <v>-65.73519999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>23.90169999999999</v>
+        <v>23.9017</v>
       </c>
       <c r="Q18" t="n">
-        <v>-482.5806</v>
+        <v>-482.5806000000001</v>
       </c>
       <c r="R18" t="n">
         <v>506.4824</v>
       </c>
       <c r="S18" t="n">
-        <v>15.17139999999999</v>
+        <v>42.9063</v>
       </c>
       <c r="T18" t="n">
-        <v>2.014399999999995</v>
+        <v>13.1656</v>
       </c>
       <c r="U18" t="n">
-        <v>13.1586</v>
+        <v>29.7408</v>
       </c>
       <c r="V18" t="n">
-        <v>-16.4582</v>
+        <v>-16.45820000000001</v>
       </c>
       <c r="W18" t="n">
         <v>241.8224</v>
